--- a/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92537338947</v>
+        <v>46157.93110818999</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110818999</v>
+        <v>46157.93365991242</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93365991242</v>
+        <v>46157.93668317886</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93668317886</v>
+        <v>46158.28192558627</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28192558627</v>
+        <v>46158.29713890711</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29713890711</v>
+        <v>46158.29787973606</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29787973606</v>
+        <v>46158.33354073501</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/02_Отчёты/02.3_Аналитика_сверки/Сводная_ведомость.xlsx
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33354073501</v>
+        <v>46158.3720964697</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
